--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Specials/Moscow/KillingPain.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Specials/Moscow/KillingPain.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Specials\Moscow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F2E920-2870-493A-91B3-82E0F40834FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D28022-D292-4C11-8C06-4CDD9953B0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8040" yWindow="1170" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="8" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -39,6 +39,10 @@
   </si>
   <si>
     <t>ResurrectCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealthRegenerationMax</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -390,7 +394,12 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Specials/Moscow/KillingPain.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Specials/Moscow/KillingPain.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Specials\Moscow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D28022-D292-4C11-8C06-4CDD9953B0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B5AD96-3BD8-494C-A16F-33FE53915484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8040" yWindow="1170" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HealthRegenerationMax</t>
+    <t>HpRegenMax</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
